--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59259-2021 artfynd.xlsx
+++ b/artfynd/A 59259-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136854364</v>
       </c>
       <c r="B2" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
